--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488173_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488173_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>L. RAMOS CASTRO</t>
+          <t>T. PERRY II</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.4237</v>
+        <v>9.918900000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>9.5242</v>
+        <v>7.844</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8995</v>
+        <v>2.0748</v>
       </c>
       <c r="G2" t="n">
-        <v>2.7877</v>
+        <v>7.6302</v>
       </c>
       <c r="H2" t="n">
-        <v>4.1579</v>
+        <v>-1.6376</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.3702</v>
+        <v>9.267799999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>2.7901</v>
+        <v>7.2786</v>
       </c>
       <c r="K2" t="n">
-        <v>5.0283</v>
+        <v>-1.1212</v>
       </c>
       <c r="L2" t="n">
-        <v>-2.2382</v>
+        <v>8.399800000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.0024</v>
+        <v>0.3516</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.8704</v>
+        <v>-0.5164</v>
       </c>
       <c r="O2" t="n">
         <v>0.868</v>
       </c>
       <c r="P2" t="n">
-        <v>0.7411</v>
+        <v>1.297</v>
       </c>
       <c r="Q2" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R2" t="n">
-        <v>1.6676</v>
+        <v>2.2234</v>
       </c>
       <c r="S2" t="n">
-        <v>2.4883</v>
+        <v>-0.8972</v>
       </c>
       <c r="T2" t="n">
-        <v>1.6813</v>
+        <v>-0.0814</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8070000000000001</v>
+        <v>-0.8158</v>
       </c>
       <c r="V2" t="n">
-        <v>4.4065</v>
+        <v>1.8888</v>
       </c>
       <c r="W2" t="n">
-        <v>5.9793</v>
+        <v>1.5733</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.5727</v>
+        <v>0.3155</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T. PERRY II</t>
+          <t>L. RAMOS CASTRO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>9.2798</v>
+        <v>8.216100000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>7.6482</v>
+        <v>8.055300000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>1.6316</v>
+        <v>0.1608</v>
       </c>
       <c r="G3" t="n">
-        <v>7.6302</v>
+        <v>2.7877</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.6376</v>
+        <v>4.1579</v>
       </c>
       <c r="I3" t="n">
-        <v>9.267799999999999</v>
+        <v>-1.3702</v>
       </c>
       <c r="J3" t="n">
-        <v>7.2786</v>
+        <v>2.7901</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.1212</v>
+        <v>5.0283</v>
       </c>
       <c r="L3" t="n">
-        <v>8.399800000000001</v>
+        <v>-2.2382</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3516</v>
+        <v>-0.0024</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.5164</v>
+        <v>-0.8704</v>
       </c>
       <c r="O3" t="n">
         <v>0.868</v>
       </c>
       <c r="P3" t="n">
-        <v>1.297</v>
+        <v>0.7411</v>
       </c>
       <c r="Q3" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R3" t="n">
-        <v>2.2234</v>
+        <v>1.6676</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.5363</v>
+        <v>0.2807</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2773</v>
+        <v>0.2124</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.259</v>
+        <v>0.0684</v>
       </c>
       <c r="V3" t="n">
-        <v>1.8888</v>
+        <v>4.4065</v>
       </c>
       <c r="W3" t="n">
-        <v>1.5733</v>
+        <v>5.9793</v>
       </c>
       <c r="X3" t="n">
-        <v>0.3155</v>
+        <v>-1.5727</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.9193</v>
+        <v>4.705</v>
       </c>
       <c r="E4" t="n">
-        <v>3.4659</v>
+        <v>3.8577</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4534</v>
+        <v>0.8473000000000001</v>
       </c>
       <c r="G4" t="n">
         <v>4.0839</v>
@@ -766,13 +766,13 @@
         <v>1.8529</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.0702</v>
+        <v>-1.2846</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.766</v>
+        <v>-0.3743</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.3042</v>
+        <v>-0.9103</v>
       </c>
       <c r="V4" t="n">
         <v>2.8321</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. GALIANO AVILA</t>
+          <t>M. CASERO MIGLIAVACCA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9115</v>
+        <v>1.1654</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.3353</v>
+        <v>0.2948</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2468</v>
+        <v>0.8706</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7935</v>
+        <v>-0.5621</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.7196</v>
+        <v>-2.3084</v>
       </c>
       <c r="I5" t="n">
-        <v>1.5131</v>
+        <v>1.7463</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.6689000000000001</v>
+        <v>0.2237</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.8763</v>
+        <v>-1.1769</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2074</v>
+        <v>1.4006</v>
       </c>
       <c r="M5" t="n">
-        <v>1.4625</v>
+        <v>-0.7858000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1567</v>
+        <v>-1.1315</v>
       </c>
       <c r="O5" t="n">
-        <v>1.3057</v>
+        <v>0.3457</v>
       </c>
       <c r="P5" t="n">
-        <v>1.6676</v>
+        <v>0.1853</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6676</v>
+        <v>2.0382</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3392</v>
+        <v>-0.9749</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6491</v>
+        <v>-0.5931</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3099</v>
+        <v>-0.3818</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.8888</v>
+        <v>2.5172</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.3155</v>
+        <v>2.5172</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.5733</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. CASERO MIGLIAVACCA</t>
+          <t>B. LEÓN TEJERA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6259</v>
+        <v>0.6221</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0969</v>
+        <v>0.6221</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7228</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.5621</v>
+        <v>0.6221</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.3084</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>1.7463</v>
+        <v>0.6221</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2237</v>
+        <v>0.6221</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.1769</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1.4006</v>
+        <v>0.6221</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7858000000000001</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.1315</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3457</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1853</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.0382</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.5144</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9849</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5295</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>2.5172</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>2.5172</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B. LEÓN TEJERA</t>
+          <t>S. GALIANO AVILA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6221</v>
+        <v>0.2741</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6221</v>
+        <v>-0.825</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1.0991</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6221</v>
+        <v>0.7935</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>-0.7196</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6221</v>
+        <v>1.5131</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6221</v>
+        <v>-0.6689000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>-0.8763</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6221</v>
+        <v>0.2074</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.4625</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>0.1567</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.3057</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.6676</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.6676</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-0.2981</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>0.1595</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>-0.4576</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.8888</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-0.3155</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.5733</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2864</v>
+        <v>0.038</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9403</v>
+        <v>1.332</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6539</v>
+        <v>-1.294</v>
       </c>
       <c r="G8" t="n">
         <v>-0.3709</v>
@@ -1078,13 +1078,13 @@
         <v>1.1117</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1577</v>
+        <v>-0.09080000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8207</v>
+        <v>-0.429</v>
       </c>
       <c r="U8" t="n">
-        <v>0.9784</v>
+        <v>0.3382</v>
       </c>
       <c r="V8" t="n">
         <v>0.3144</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1623</v>
+        <v>0.0168</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.5503</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7796999999999999</v>
+        <v>-0.5335</v>
       </c>
       <c r="G9" t="n">
         <v>-2.1628</v>
@@ -1156,13 +1156,13 @@
         <v>0.9264</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1393</v>
+        <v>-0.0062</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7586000000000001</v>
+        <v>0.3669</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6193</v>
+        <v>-0.3731</v>
       </c>
       <c r="V9" t="n">
         <v>1.2594</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.5347</v>
+        <v>-2.7496</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.9507</v>
+        <v>-2.461</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.584</v>
+        <v>-0.2886</v>
       </c>
       <c r="G10" t="n">
         <v>0.8921</v>
@@ -1234,13 +1234,13 @@
         <v>0.9264</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0366</v>
+        <v>-0.2515</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7113</v>
+        <v>-0.2216</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3253</v>
+        <v>-0.0299</v>
       </c>
       <c r="V10" t="n">
         <v>0.3155</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.1634</v>
+        <v>-5.6738</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.4719</v>
+        <v>-3.9823</v>
       </c>
       <c r="F11" t="n">
         <v>-1.6915</v>
@@ -1312,10 +1312,10 @@
         <v>1.4823</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2634</v>
+        <v>-0.7738</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0396</v>
+        <v>-0.5499000000000001</v>
       </c>
       <c r="U11" t="n">
         <v>-0.2239</v>
@@ -1345,7 +1345,7 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>16.5329</v>
+        <v>16.533</v>
       </c>
       <c r="E12" t="n">
         <v>15.2879</v>
@@ -1354,7 +1354,7 @@
         <v>1.245</v>
       </c>
       <c r="G12" t="n">
-        <v>9.813699999999999</v>
+        <v>9.813699999999997</v>
       </c>
       <c r="H12" t="n">
         <v>-4.8163</v>
@@ -1378,7 +1378,7 @@
         <v>-9.864800000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>3.457100000000001</v>
+        <v>3.4571</v>
       </c>
       <c r="P12" t="n">
         <v>-3.885780586188048e-16</v>
@@ -1390,13 +1390,13 @@
         <v>13.8965</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.296399999999999</v>
+        <v>-4.2964</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.5108</v>
+        <v>-1.5105</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.7857</v>
+        <v>-2.7858</v>
       </c>
       <c r="V12" t="n">
         <v>11.0157</v>
@@ -1405,7 +1405,7 @@
         <v>14.4741</v>
       </c>
       <c r="X12" t="n">
-        <v>-3.458299999999999</v>
+        <v>-3.4583</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.2287</v>
+        <v>2.2729</v>
       </c>
       <c r="E13" t="n">
-        <v>4.6001</v>
+        <v>3.8167</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.3714</v>
+        <v>-1.5438</v>
       </c>
       <c r="G13" t="n">
         <v>3.3431</v>
@@ -1468,13 +1468,13 @@
         <v>1.4823</v>
       </c>
       <c r="S13" t="n">
-        <v>1.8474</v>
+        <v>0.8915999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>0.9737</v>
+        <v>0.1903</v>
       </c>
       <c r="U13" t="n">
-        <v>0.8737</v>
+        <v>0.7013</v>
       </c>
       <c r="V13" t="n">
         <v>-2.5177</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. JIMENEZ HERRERA</t>
+          <t>I. LLANO ABASCAL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.2253</v>
+        <v>2.111</v>
       </c>
       <c r="E14" t="n">
-        <v>1.8158</v>
+        <v>2.1654</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4095</v>
+        <v>-0.0545</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.2426</v>
+        <v>2.4928</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1381</v>
+        <v>1.1472</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.3807</v>
+        <v>1.3456</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.06510000000000001</v>
+        <v>2.1241</v>
       </c>
       <c r="K14" t="n">
-        <v>1.2406</v>
+        <v>0.7554999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.3057</v>
+        <v>1.3686</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.1775</v>
+        <v>0.3687</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.1026</v>
+        <v>0.3917</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.075</v>
+        <v>-0.023</v>
       </c>
       <c r="P14" t="n">
-        <v>0.3706</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R14" t="n">
-        <v>1.297</v>
+        <v>0.9264</v>
       </c>
       <c r="S14" t="n">
-        <v>2.5791</v>
+        <v>0.877</v>
       </c>
       <c r="T14" t="n">
-        <v>0.919</v>
+        <v>0.9678</v>
       </c>
       <c r="U14" t="n">
-        <v>1.6601</v>
+        <v>-0.09080000000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>2.5183</v>
+        <v>-1.2589</v>
       </c>
       <c r="W14" t="n">
-        <v>1.8883</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0.63</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>I. LLANO ABASCAL</t>
+          <t>D. JIMENEZ HERRERA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.14</v>
+        <v>1.7284</v>
       </c>
       <c r="E15" t="n">
-        <v>3.0468</v>
+        <v>0.9344</v>
       </c>
       <c r="F15" t="n">
-        <v>0.09320000000000001</v>
+        <v>0.794</v>
       </c>
       <c r="G15" t="n">
-        <v>2.4928</v>
+        <v>-2.2426</v>
       </c>
       <c r="H15" t="n">
-        <v>1.1472</v>
+        <v>0.1381</v>
       </c>
       <c r="I15" t="n">
-        <v>1.3456</v>
+        <v>-2.3807</v>
       </c>
       <c r="J15" t="n">
-        <v>2.1241</v>
+        <v>-0.06510000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>0.7554999999999999</v>
+        <v>1.2406</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3686</v>
+        <v>-1.3057</v>
       </c>
       <c r="M15" t="n">
-        <v>0.3687</v>
+        <v>-2.1775</v>
       </c>
       <c r="N15" t="n">
-        <v>0.3917</v>
+        <v>-1.1026</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.023</v>
+        <v>-1.075</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>0.3706</v>
       </c>
       <c r="Q15" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9264</v>
+        <v>1.297</v>
       </c>
       <c r="S15" t="n">
-        <v>1.9061</v>
+        <v>1.0822</v>
       </c>
       <c r="T15" t="n">
-        <v>1.8492</v>
+        <v>0.0376</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0569</v>
+        <v>1.0445</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.2589</v>
+        <v>2.5183</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.8883</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.2589</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.3306</v>
+        <v>-0.3267</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9619</v>
+        <v>1.9412</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.2925</v>
+        <v>-2.2679</v>
       </c>
       <c r="G16" t="n">
         <v>-2.2325</v>
@@ -1702,13 +1702,13 @@
         <v>1.8529</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9859</v>
+        <v>0.018</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.3132</v>
+        <v>-0.3339</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3273</v>
+        <v>0.3519</v>
       </c>
       <c r="V16" t="n">
         <v>1.8877</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>F. RUESGA MORALES</t>
+          <t>J. CARBU RODRIGUEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.3314</v>
+        <v>-2.1098</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0635</v>
+        <v>-0.9296</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.2678</v>
+        <v>-1.1801</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2382</v>
+        <v>-1.089</v>
       </c>
       <c r="H17" t="n">
-        <v>2.0154</v>
+        <v>-0.0354</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.7771</v>
+        <v>-1.0536</v>
       </c>
       <c r="J17" t="n">
-        <v>2.7689</v>
+        <v>0.2158</v>
       </c>
       <c r="K17" t="n">
-        <v>2.7262</v>
+        <v>0.1329</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0427</v>
+        <v>0.0829</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.5307</v>
+        <v>-1.3048</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7108</v>
+        <v>-0.1683</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.8198</v>
+        <v>-1.1366</v>
       </c>
       <c r="P17" t="n">
+        <v>0.1853</v>
+      </c>
+      <c r="Q17" t="n">
         <v>-0.9264</v>
       </c>
-      <c r="Q17" t="n">
-        <v>-3.7057</v>
-      </c>
       <c r="R17" t="n">
-        <v>2.7793</v>
+        <v>1.1117</v>
       </c>
       <c r="S17" t="n">
-        <v>1.1901</v>
+        <v>0.0529</v>
       </c>
       <c r="T17" t="n">
-        <v>1.1889</v>
+        <v>0.411</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0012</v>
+        <v>-0.3581</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.8332</v>
+        <v>-1.2589</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.3155</v>
+        <v>-0.63</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.5177</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. CARBU RODRIGUEZ</t>
+          <t>F. RUESGA MORALES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.4041</v>
+        <v>-2.6</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.1255</v>
+        <v>-0.4552</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.2786</v>
+        <v>-2.1447</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.089</v>
+        <v>0.2382</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0354</v>
+        <v>2.0154</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.0536</v>
+        <v>-1.7771</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2158</v>
+        <v>2.7689</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1329</v>
+        <v>2.7262</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0829</v>
+        <v>0.0427</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.3048</v>
+        <v>-2.5307</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1683</v>
+        <v>-0.7108</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.1366</v>
+        <v>-1.8198</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1853</v>
+        <v>-0.9264</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9264</v>
+        <v>-3.7057</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1117</v>
+        <v>2.7793</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2415</v>
+        <v>0.9215</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2151</v>
+        <v>0.7971</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4566</v>
+        <v>0.1243</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.2589</v>
+        <v>-2.8332</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.63</v>
+        <v>-0.3155</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.6289</v>
+        <v>-2.5177</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.6564</v>
+        <v>-2.6072</v>
       </c>
       <c r="E19" t="n">
         <v>-0.08799999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.5685</v>
+        <v>-2.5192</v>
       </c>
       <c r="G19" t="n">
         <v>-0.6921</v>
@@ -1936,13 +1936,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0766</v>
+        <v>-0.0274</v>
       </c>
       <c r="T19" t="n">
         <v>-0.1094</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0328</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="V19" t="n">
         <v>-1.8877</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.1624</v>
+        <v>-3.1321</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.85</v>
+        <v>-2.1645</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.3123</v>
+        <v>-0.9676</v>
       </c>
       <c r="G20" t="n">
         <v>-1.5839</v>
@@ -2014,13 +2014,13 @@
         <v>1.297</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7638</v>
+        <v>0.2664</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6019</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1619</v>
+        <v>0.1828</v>
       </c>
       <c r="V20" t="n">
         <v>-1.2589</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.9193</v>
+        <v>-4.8409</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.7646</v>
+        <v>-1.8832</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.1546</v>
+        <v>-2.9577</v>
       </c>
       <c r="G21" t="n">
         <v>-2.3337</v>
@@ -2092,13 +2092,13 @@
         <v>1.4823</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.3087</v>
+        <v>-0.2304</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9302</v>
+        <v>-0.0488</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3785</v>
+        <v>-0.1816</v>
       </c>
       <c r="V21" t="n">
         <v>-2.8327</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-7.3229</v>
+        <v>-7.0286</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.778</v>
+        <v>-4.5822</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.5449</v>
+        <v>-2.4464</v>
       </c>
       <c r="G22" t="n">
         <v>-5.714</v>
@@ -2170,13 +2170,13 @@
         <v>1.6676</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1502</v>
+        <v>0.4446</v>
       </c>
       <c r="T22" t="n">
-        <v>0.5944</v>
+        <v>0.7903</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4442</v>
+        <v>-0.3457</v>
       </c>
       <c r="V22" t="n">
         <v>-1.5738</v>
@@ -2203,16 +2203,16 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-16.5331</v>
+        <v>-16.533</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.244999999999999</v>
+        <v>-1.245000000000001</v>
       </c>
       <c r="F23" t="n">
         <v>-15.2879</v>
       </c>
       <c r="G23" t="n">
-        <v>-9.813700000000001</v>
+        <v>-9.813699999999999</v>
       </c>
       <c r="H23" t="n">
         <v>4.8164</v>
@@ -2221,7 +2221,7 @@
         <v>-14.6298</v>
       </c>
       <c r="J23" t="n">
-        <v>6.407599999999999</v>
+        <v>6.4076</v>
       </c>
       <c r="K23" t="n">
         <v>9.8649</v>
@@ -2251,16 +2251,16 @@
         <v>4.2964</v>
       </c>
       <c r="T23" t="n">
-        <v>2.785600000000001</v>
+        <v>2.7856</v>
       </c>
       <c r="U23" t="n">
-        <v>1.5108</v>
+        <v>1.5107</v>
       </c>
       <c r="V23" t="n">
         <v>-11.0158</v>
       </c>
       <c r="W23" t="n">
-        <v>3.458200000000001</v>
+        <v>3.4582</v>
       </c>
       <c r="X23" t="n">
         <v>-14.4741</v>
